--- a/samples/CopilotCheck_demo.en.xlsx
+++ b/samples/CopilotCheck_demo.en.xlsx
@@ -51,7 +51,7 @@
     <t>Run date</t>
   </si>
   <si>
-    <t>2026-08-15 13:20:10</t>
+    <t>2026-08-15 13:54:29</t>
   </si>
   <si>
     <t>Duration (seconds)</t>
@@ -204,7 +204,7 @@
     <t>Licensing</t>
   </si>
   <si>
-    <t>Assign an M365 E3/E5 or Business Premium licence to the target users</t>
+    <t>M365 E3/E5 or Business Premium licence assigned to the target users</t>
   </si>
   <si>
     <t>Observed value matches the target</t>
@@ -229,7 +229,7 @@
     <t>https://learn.microsoft.com/microsoft-365/admin/manage/assign-licenses-to-users</t>
   </si>
   <si>
-    <t>Purchase the Microsoft 365 Copilot SKU and confirm it is visible on the tenant</t>
+    <t>Microsoft 365 Copilot SKU purchased and visible on the tenant</t>
   </si>
   <si>
     <t>Gap against the expected value</t>
@@ -251,10 +251,10 @@
 5. After purchase: Billing &gt; Licences &gt; check that 'Microsoft 365 Copilot' appears in the list</t>
   </si>
   <si>
-    <t>Get-MgSubscribedSku | Where {$_.SkuPartNumber -like '*COPILOT*'} | Select SkuPartNumber, @{N='Dispo';E={$_.PrepaidUnits.Enabled - $_.ConsumedUnits}}</t>
-  </si>
-  <si>
-    <t>Assign the Copilot licence individually or through a group</t>
+    <t>Get-MgSubscribedSku | Where {$_.SkuPartNumber -like '*COPILOT*'} | Select SkuPartNumber, @{N='Available';E={$_.PrepaidUnits.Enabled - $_.ConsumedUnits}}</t>
+  </si>
+  <si>
+    <t>Copilot licence assigned individually or through a group</t>
   </si>
   <si>
     <t>Every target user has the Copilot licence ticked</t>
@@ -278,7 +278,7 @@
     <t>Get-MgUserLicenseDetail -UserId 'user@domain.com' | Select SkuPartNumber</t>
   </si>
   <si>
-    <t>Assign licences through an Entra ID group rather than manually</t>
+    <t>Licences assigned through an Entra ID group (not manually)</t>
   </si>
   <si>
     <t>Partial configuration: a decision is required</t>
@@ -332,7 +332,7 @@
     <t>Office apps</t>
   </si>
   <si>
-    <t>Deploy Microsoft 365 Apps for enterprise on the workstations</t>
+    <t>Microsoft 365 Apps for enterprise deployed on the workstations</t>
   </si>
   <si>
     <t>Manual verification required (no public API)</t>
@@ -363,7 +363,7 @@
     <t>https://learn.microsoft.com/deployoffice/about-microsoft-365-apps</t>
   </si>
   <si>
-    <t>Set the update channel to Current Channel or Monthly Enterprise Channel</t>
+    <t>Update channel = Current Channel or Monthly Enterprise</t>
   </si>
   <si>
     <t>Channel = Current Channel or Monthly Enterprise Channel</t>
@@ -395,7 +395,7 @@
     <t>https://learn.microsoft.com/deployoffice/updates/overview-update-channels</t>
   </si>
   <si>
-    <t>Enable Modern Authentication (OAuth2) on the tenant</t>
+    <t>Modern Authentication (OAuth2) enabled on the tenant</t>
   </si>
   <si>
     <t>OAuth2ClientProfileEnabled = True</t>
@@ -420,7 +420,7 @@
     <t>https://learn.microsoft.com/exchange/clients-and-mobile-in-exchange-online/enable-or-disable-modern-authentication-in-exchange-online</t>
   </si>
   <si>
-    <t>Enable connected experiences</t>
+    <t>Connected experiences enabled</t>
   </si>
   <si>
     <t>Connected experiences = Enabled (all 3 categories)</t>
@@ -460,7 +460,7 @@
     <t>Conditional access policy enabled, targeting the Copilot group with mandatory MFA</t>
   </si>
   <si>
-    <t>Copilot considerably amplifies the risk posed by a compromised account: an attacker can use Copilot to query all of the victim's M365 data in natural language (emails, files, Teams conversations) in a matter of seconds, where doing it manually would take hours. MFA (multi-factor authentication) blocks 99.9 percent of account compromise attempts according to Microsoft. Without MFA, a single stolen or guessed password grants full access to Copilot and to every piece of data the user is able to view, turning Copilot into a mass exfiltration tool for the attacker.</t>
+    <t>Copilot considerably amplifies the risk posed by a compromised account: an attacker can use Copilot to query all of the victim's M365 data in natural language (emails, files, Teams conversations) in a matter of seconds, where doing it manually would take hours. MFA (multi-factor authentication) blocks 99.9 per cent of account compromise attempts according to Microsoft. Without MFA, a single stolen or guessed password grants full access to Copilot and to every piece of data the user is able to view, turning Copilot into a mass exfiltration tool for the attacker.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open https://entra.microsoft.com
@@ -551,7 +551,7 @@
     <t>0 disabled accounts holding a Copilot licence</t>
   </si>
   <si>
-    <t>Every Copilot licence assigned to a disabled account is a direct waste of 30 USD per month with no benefit whatsoever to the organisation. These needlessly consumed licences reduce the number of licences available to active staff who could genuinely make use of them. On top of that, a disabled but licensed account is a security risk: if it is re-enabled by mistake or compromised, the attacker immediately has Copilot at their disposal to explore the data. Without regular clean-up, the costs accumulate and can amount to thousands of dollars a year.</t>
+    <t>Every Copilot licence assigned to a disabled account is a direct waste of USD 30 per month with no benefit whatsoever to the organisation. These needlessly consumed licences reduce the number of licences available to active staff who could genuinely make use of them. On top of that, a disabled but licensed account is a security risk: if it is re-enabled by mistake or compromised, the attacker immediately has Copilot at their disposal to explore the data. Without regular clean-up, the costs accumulate and can amount to thousands of dollars a year.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open https://entra.microsoft.com
@@ -698,7 +698,7 @@
     <t>https://learn.microsoft.com/sharepoint/pre-provision-accounts</t>
   </si>
   <si>
-    <t>Verify that Microsoft Search is enabled and working</t>
+    <t>Check that Microsoft Search is enabled and working</t>
   </si>
   <si>
     <t>Microsoft Search enabled with SPO + OneDrive + Exchange indexed</t>
@@ -725,7 +725,7 @@
     <t>https://learn.microsoft.com/microsoftsearch/overview-microsoft-search</t>
   </si>
   <si>
-    <t>Verify that NoCrawl is disabled on critical sites</t>
+    <t>Check that NoCrawl is disabled on critical sites</t>
   </si>
   <si>
     <t>NoCrawl = False on all important sites</t>
@@ -740,7 +740,7 @@
 3. For each critical site (HR, Finance, Projects): click &gt; Properties
 4. Check that indexing is enabled
 --- OR via PnP PowerShell ---
-1. Connect-PnPOnline -Url https://tenant.sharepoint.com/sites/SiteCritique -Interactive
+1. Connect-PnPOnline -Url https://tenant.sharepoint.com/sites/CriticalSite -Interactive
 2. Get-PnPWeb -Includes NoCrawl
 3. If NoCrawl = True: Set-PnPWeb -NoCrawl $false</t>
   </si>
@@ -751,7 +751,7 @@
     <t>https://learn.microsoft.com/sharepoint/crawl-site-content</t>
   </si>
   <si>
-    <t>Verify the Restricted SharePoint Search configuration</t>
+    <t>Check the Restricted SharePoint Search configuration</t>
   </si>
   <si>
     <t>Restricted Search disabled OR all critical sites explicitly included</t>
@@ -926,7 +926,7 @@
     <t>Microsoft 365 Copilot pinned to the app bar</t>
   </si>
   <si>
-    <t>Pinning Copilot to the Teams app bar makes it visible and one click away for every user, with no need to hunt for it in the app catalogue. Adoption data shows that pinning increases Copilot usage by 40 to 60 percent compared with a deployment without pinning. Without this configuration, the majority of users never discover the Copilot app in Teams and never use the cross-application chat features, which are nonetheless the most powerful use case. Placing Copilot at the top of the app bar maximises its visibility and the return on investment of the licences.</t>
+    <t>Pinning Copilot to the Teams app bar makes it visible and one click away for every user, with no need to hunt for it in the app catalogue. Adoption data shows that pinning increases Copilot usage by 40 to 60 per cent compared with a deployment without pinning. Without this configuration, the majority of users never discover the Copilot app in Teams and never use the cross-application chat features, which are nonetheless the most powerful use case. Placing Copilot at the top of the app bar maximises its visibility and the return on investment of the licences.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open https://admin.teams.microsoft.com
@@ -1140,7 +1140,7 @@
     <t>https://learn.microsoft.com/copilot/microsoft-365/manage-public-web-access</t>
   </si>
   <si>
-    <t>Verify Copilot propagation on a test user</t>
+    <t>Check Copilot propagation on a test user</t>
   </si>
   <si>
     <t>Copilot visible in Word, Outlook, Teams and Chat for the test user</t>
@@ -1154,7 +1154,7 @@
 3. Sign in as that user
 4. Open Word &gt; Check the Copilot button in the ribbon
 5. Open Outlook &gt; Check the Copilot icon
-6. Open Teams &gt; Check the Copilot app in the side bar
+6. Open Teams &gt; Check the Copilot app in the app bar
 7. Open https://copilot.microsoft.com &gt; Check access to Chat</t>
   </si>
   <si>
@@ -1196,7 +1196,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Open https://insights.viva.office.com
-   (or via https://admin.cloud.microsoft &gt; Admin centers &gt; Viva)
+   (or via https://admin.cloud.microsoft &gt; Admin centres &gt; Viva)
 2. 'Copilot dashboard' section
 3. Check that Copilot data is being collected
 4. Configure the analysis segments by department
@@ -1270,7 +1270,7 @@
 7. Save</t>
   </si>
   <si>
-    <t>Via admin.cloud.microsoft &gt; Copilot &gt; Settings &gt; Disclaimer</t>
+    <t>Via admin.cloud.microsoft &gt; Copilot &gt; Settings &gt; AI disclaimer</t>
   </si>
   <si>
     <t>Agents</t>
@@ -5171,7 +5171,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="43.440216064453125" customWidth="1"/>
-    <col min="3" max="3" width="69.45165252685547" customWidth="1"/>
+    <col min="3" max="3" width="62.67180252075195" customWidth="1"/>
     <col min="4" max="4" width="14.526350021362305" customWidth="1"/>
     <col min="5" max="5" width="28.389907836914062" customWidth="1"/>
   </cols>

--- a/samples/CopilotCheck_demo.en.xlsx
+++ b/samples/CopilotCheck_demo.en.xlsx
@@ -51,7 +51,7 @@
     <t>Run date</t>
   </si>
   <si>
-    <t>2026-08-15 22:04:08</t>
+    <t>2026-08-16 11:58:40</t>
   </si>
   <si>
     <t>Duration (seconds)</t>

--- a/samples/CopilotCheck_demo.en.xlsx
+++ b/samples/CopilotCheck_demo.en.xlsx
@@ -51,7 +51,7 @@
     <t>Run date</t>
   </si>
   <si>
-    <t>2026-08-16 11:58:40</t>
+    <t>2026-08-16 12:11:39</t>
   </si>
   <si>
     <t>Duration (seconds)</t>
@@ -3175,7 +3175,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="0">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">

--- a/samples/CopilotCheck_demo.en.xlsx
+++ b/samples/CopilotCheck_demo.en.xlsx
@@ -51,7 +51,7 @@
     <t>Run date</t>
   </si>
   <si>
-    <t>2026-08-16 12:11:39</t>
+    <t>2026-08-16 14:36:05</t>
   </si>
   <si>
     <t>Duration (seconds)</t>
@@ -3175,7 +3175,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="0">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">

--- a/samples/CopilotCheck_demo.en.xlsx
+++ b/samples/CopilotCheck_demo.en.xlsx
@@ -2856,7 +2856,7 @@
     <t>Message</t>
   </si>
   <si>
-    <t>14:57:42</t>
+    <t>15:23:33</t>
   </si>
   <si>
     <t>INFO</t>
@@ -2868,7 +2868,7 @@
     <t>Microsoft 365 Copilot - Tenant configuration status</t>
   </si>
   <si>
-    <t xml:space="preserve">Contoso Demo  ·  00000000-1111-2222-3333-444444444444  ·  generated on 16-08-2026 14:57  ·  EN</t>
+    <t xml:space="preserve">Contoso Demo  ·  00000000-1111-2222-3333-444444444444  ·  generated on 16-08-2026 15:23  ·  EN</t>
   </si>
   <si>
     <t>65 %</t>
@@ -3405,7 +3405,7 @@
     </xdr:to>
     <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chartza55jo"/>
+        <xdr:cNvPr id="0" name="Chart2stotj"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
